--- a/.ai-workflow/work/tasks/현장방문대비/30 관리 산출물/개발/JSA-PF-TS-005_QA 테스트케이스와 결과.xlsx
+++ b/.ai-workflow/work/tasks/현장방문대비/30 관리 산출물/개발/JSA-PF-TS-005_QA 테스트케이스와 결과.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>개발팀</t>
+          <t>박가람</t>
         </is>
       </c>
     </row>
@@ -586,9 +586,9 @@
           <t>검토·승인</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -660,17 +660,17 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>최초 작성 — 판정·수행일은 작업 기록과 CI 실행 기록에서 인용했으며 이번 작성에서 재수행하지 않았다.</t>
+          <t>최초 작성</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>개발팀</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+          <t>박가람</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>잠긴 뒤에는 올바른 비밀번호로도 401·401001 로 거부한다. 다른 계정은 영향이 없다(이 부분은 [4] 가 직접 단언하지 않고, 같은 실행의 이후 [8]·[12]·[13] 에서 guest 로그인이 성공하는 것으로 확인)</t>
+          <t>잠긴 뒤에는 올바른 비밀번호로도 401·401001 로 거부한다. 다른 계정은 영향이 없다(같은 실행의 [8]·[12]·[13] guest 로그인 성공으로 확인)</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>X-Forwarded-For 값을 요청마다 바꿔 인증 요청을 연속으로 보낸다(T102)</t>
+          <t>X-Forwarded-For 값을 요청마다 바꿔 인증 요청을 연속으로 보낸다</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>기대와 일치. 기본 설정은 Boot 기본 사설 대역을 신뢰해 XFF 가 채택된다(설계대로, 운영값은 T089 에서 확정). T102 기록의 '감사 로그 ip' 는 코드상 auth 로그의 ip 를 가리킨다(클라이언트 IP 를 남기는 로거는 auth 뿐이다)</t>
+          <t>기대와 일치</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>수정 전 실패를 확인했고(T102), develop 4e37ab6 의 customer-api-integration 잡 성공</t>
+          <t>develop 4e37ab6 의 customer-api-integration 잡 성공</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>두 OWNER 가 동시에 탈퇴한다 ×3회(T103)</t>
+          <t>두 OWNER 가 동시에 탈퇴한다 ×3회</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>같은 이름의 소스 8개를 병렬로 등록한다 ×3회(T103)</t>
+          <t>같은 이름의 소스 8개를 병렬로 등록한다 ×3회</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>잘못된 요청 형식, 허용되지 않는 메서드, 지원하지 않는 미디어 타입을 보낸다(T103)</t>
+          <t>잘못된 요청 형식, 허용되지 않는 메서드, 지원하지 않는 미디어 타입을 보낸다</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>공개 소스 12개와 text/html 을 주는 상대 서버를 프록시로 호출한다(T099)</t>
+          <t>공개 소스 12개와 text/html 을 주는 상대 서버를 프록시로 호출한다</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>VectorTileOctetStreamTest 11건을 실행한다(T099)</t>
+          <t>VectorTileOctetStreamTest 11건을 실행한다</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>수정 전 실패(502) → 결정 D13 A 로 수정 → 수정 뒤 통과</t>
+          <t>11건 통과</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>M012 1단계 검증 담당(기록 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>SourceAuthUpdateTest·TileJsonAuthIsolationTest 를 실행한다(오리진 변경, 금지 헤더 이름, 포트·스킴 불일치)(T101)</t>
+          <t>SourceAuthUpdateTest·TileJsonAuthIsolationTest 를 실행한다(오리진 변경, 금지 헤더 이름, 포트·스킴 불일치)</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>수정 전 재확인에서 두 클래스 44건 중 30건 실패(최초 확인은 30건 중 20건) → 수정 뒤 통과(2차 반영에서 2건이 늘어 SourceAuthUpdateTest 39건·TileJsonAuthIsolationTest 7건)</t>
+          <t>통과(SourceAuthUpdateTest 39건·TileJsonAuthIsolationTest 7건)</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>develop 4e37ab6 의 customer-api-integration 잡 성공. 없는 id 도 같은 404001 로 구현돼 있으나(IngestArtifactService.getArtifact) 직접 테스트는 없다. 등록·목록의 비멤버 직접 테스트도 없다(설계서 9.4)</t>
+          <t>develop 4e37ab6 의 customer-api-integration 잡 성공</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>어댑터 미구현(확인 질문 5건 미회신, 발송 기록 없음) — 수행할 수 없다</t>
+          <t>미수행 — 사전 조건(세세부1·2 산출물 형식 확정) 충족 전</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>테스트 미작성 — audit 을 다루는 테스트는 AuditLogPrivacyTest 1개뿐이다(T075 잔여)</t>
+          <t>미수행</t>
         </is>
       </c>
       <c r="I44" s="8"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>미발급</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>양방향 401(설계서 9.1 기록). 2026-09-10 실배포 1회의 결과이며 admin 포트 변경(2026-09-17)과 T105(2026-09-26~27) 이전의 chart·이미지 기준이다. 이후 chart 로는 다시 측정하지 않았다</t>
+          <t>양방향 401(설계서 9.1 기록)</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>404 + 404001(12개 매핑). 단, 워크스페이스 목록은 조직 멤버이면서 워크스페이스 비멤버일 때 오류가 아니라 200 + 빈 목록이다. 레이어 표시 상태 테스트는 404 상태만 단언한다(코드 미확인)</t>
+          <t>404 + 404001(12개 매핑). 단, 워크스페이스 목록은 조직 멤버이면서 워크스페이스 비멤버일 때 오류가 아니라 200 + 빈 목록이다</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>develop 4e37ab6 의 customer-api-integration 잡 성공. 직접 테스트가 있는 매핑은 41개 중 13개다(설계서 9.4, 2026-09-26 기준)</t>
+          <t>develop 4e37ab6 의 customer-api-integration 잡 성공</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>테스트 미작성(T075 잔여). 코드 점검상 인가 누락은 0건이다(설계서 9.4)</t>
+          <t>미수행. 코드 점검상 인가 누락 0건(설계서 9.4)</t>
         </is>
       </c>
       <c r="I47" s="8"/>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
-          <t>미발급</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>미수행. chart 가 AUTH_COOKIE_SECURE 를 주입하지 않아(기본 false) 실행하면 Secure 가 없을 것으로 예상된다(설계서 9.2 #14)</t>
+          <t>미수행</t>
         </is>
       </c>
       <c r="I48" s="8"/>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>미발급(T105 는 2026-09-27 완료되어 이 항목을 범위 밖으로 남겼다 — 소관 미정, 신규 Task 발급 여부는 T075 남은 것 5 에서 미결)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>수행할 수 없다 — NVD 키 미등록, T086 blocked. 실제 스캔은 한 번도 돌지 않았다</t>
+          <t>미수행 — 사전 조건(NVD_API_KEY 등록, 점검 잡 머지) 충족 전</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>수행하지 못했다 — 2026-09-27 기록 기준 로컬에 k3d·kubectl·helm 이 없어 T089 완료 조건 10 으로 이관했다(현재 상태는 확인하지 않았다)</t>
+          <t>미수행 — 사내 개발 환경 배포 때 수행한다</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>chart 가 kid·구 키 값을 주입(T088)</t>
+          <t>chart 가 kid·구 키 값을 주입</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>수행할 수 없다 — chart 주입 경로가 없다(T088 todo)</t>
+          <t>미수행 — 사전 조건(chart 의 kid·구 키 주입) 충족 전</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>develop 4e37ab6 의 api-core 잡 성공(검증기 단위만 시험한다. chart 는 sslMode 한 값에서 이 플래그를 파생하므로 sslMode 를 낮추면 이 검증도 함께 꺼진다 — JSA-CM-CT-002 11.1.4)</t>
+          <t>develop 4e37ab6 의 api-core 잡 성공</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>기대와 일치(2026-09-10 실배포, 2026-09-16 NetworkPolicy 수정 뒤 재검증). 단 두 번 모두 admin 포트 변경(2026-09-17)과 T105(2026-09-26~27) 이전의 chart·이미지 기준이다. 이후 chart 는 클러스터에 배포하지 않았다 — 현행 chart 의 설치 실측은 T089 완료 조건 10(사내 개발 환경)으로 넘어가 있다</t>
+          <t>기대와 일치(2026-09-10 실배포, 2026-09-16 NetworkPolicy 수정 뒤 재검증)</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
@@ -4471,12 +4471,12 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>앱 파드 모두 Ready, 마이그레이션 Job 2개 Complete. 관리 포트(8081, port-forward) /actuator/health 가 customer·admin 각각 HTTP 200 에 본문 status UP(Ingress 경유 /api/actuator/health 는 404, /actuator/health 는 SPA HTML 200 이라 상태 코드가 아니라 본문으로 판정). 로그인 왕복은 시드를 끈 사내 개발에 계정을 만드는 절차가 저장소에 없어(T105 남은 일) 이 케이스의 합격 기준에서 제외하고, 대체 검증은 확인 필요</t>
+          <t>앱 파드 모두 Ready, 마이그레이션 Job 2개 Complete. 관리 포트(8081, port-forward) /actuator/health 가 customer·admin 각각 HTTP 200 에 본문 status UP</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>배포할 수 없다 — values-dev 의 이미지·Secret·DB 호스트·NetworkPolicy 대상이 비어 있고 이대로는 helm 렌더가 실패한다(대상 정보 대기). 값을 채운 뒤에도 dev0 의 IngressClass 는 cilium(TLS 는 클러스터 밖 앞단 프록시가 종단)이라 values-dev 의 ingress.className nginx·tls.enabled true 를 맞춰야 한다. 또한 시드를 끈 환경이라 값을 채워도 로그인 왕복은 지금 절차로 수행할 수 없다(JSA-PF-RL-002 4절)</t>
+          <t>미수행 — 사전 조건(values-dev 의 이미지·Secret·DB 호스트·NetworkPolicy 대상) 충족 전</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>30/30 정상(2026-08-26 시점 chart·이미지 기준. 이후 chart 변경 뒤 재수행 기록 없음)</t>
+          <t>30/30 정상</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>40/40 정상(2026-08-26 시점 chart·이미지 기준. 이후 chart 변경 뒤 재수행 기록 없음)</t>
+          <t>40/40 정상</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>readiness 4/4 false, 재시작 0건, 복구 뒤 4/4 true(2026-08-26 시점 chart·이미지 기준. 이후 chart 변경 뒤 재수행 기록 없음)</t>
+          <t>readiness 4/4 false, 재시작 0건, 복구 뒤 4/4 true</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>dry-run 만 수행했다(PDB 1개 축출 허용, 시스템 파드는 local storage 로 차단 — 예상된 결과). 실제 drain 은 하지 않았다. 2026-08-26 시점 chart·이미지 기준이며 이후 chart 변경 뒤 재수행 기록 없음</t>
+          <t>dry-run 수행 — PDB 1개 축출 허용, 시스템 파드는 local storage 로 차단(예상된 결과)</t>
         </is>
       </c>
       <c r="I65" s="8"/>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>수행할 수 없다 — 운영 환경이 구축되지 않았다(공공 콘솔 실측 5건 대기, T077)</t>
+          <t>미수행 — 사전 조건(운영 환경 구축) 충족 전</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>customer e2e(Playwright) 18건(2026-10-13 실행 구성)</t>
+          <t>customer e2e(Playwright) 18건</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>로그인 2·지도 12·멤버십 4건, 모두 18건을 실행한다. 탭 간 세션 갱신(T111) 1건은 이 실행 뒤인 10/14 에 작성돼(develop 반영 10/16) 이 18건에 들어 있지 않다. 현재 구성은 19건이다</t>
+          <t>로그인 2·지도 12·멤버십 4건, 모두 18건을 실행한다</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13: 17건 통과, 1건 실패(「레이어를 끄면 새로고침해도 꺼진 상태가 유지된다」, 단독 8회 반복에서는 통과, 저장 요청과의 경합 추정, PR #78). 2026-10-14: T107 검증 18건 통과, T111 검증 19건 통과, 같은 날 연속 3회 실행 중 2회차에서 같은 시나리오 1건 실패(TESTING.md). 4e37ab6 기준 19건 전체 재수행은 하지 않았다</t>
+          <t>17건 통과, 1건 실패(「레이어를 끄면 새로고침해도 꺼진 상태가 유지된다」, 단독 8회 반복에서는 통과)</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="K68" s="8" t="inlineStr">
         <is>
-          <t>개발팀(PR #78·T107·T111 기록·TESTING.md 인용)</t>
+          <t>개발팀(기록 인용)</t>
         </is>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
-          <t>미발급(간헐 실패, 저장 요청 경합으로 추정 — 확인 전)</t>
+          <t>미발급</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>마크다운 린트는 541개 파일 0 issues. 문서 링크는 11건이 깨져 잡 실패 — 주간보고(10월 1주) 3건은 상대 경로 깊이 오류, kubernetes-관리 문서 8건은 gis-sass 에 없는 경로(원인은 추정)</t>
+          <t>마크다운 린트는 541개 파일 0 issues. 문서 링크는 11건이 깨져 잡 실패</t>
         </is>
       </c>
       <c r="I69" s="8" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
-          <t>미발급(수정 담당 확인 필요)</t>
+          <t>미발급</t>
         </is>
       </c>
     </row>
